--- a/static/standards-correlations/Georgia_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/Georgia_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$64</definedName>
@@ -565,10 +565,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | GaDOE CTAE Information Technology cluster - judge on IT-CSP-2 to 8</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | GaDOE CTAE Information Technology cluster - judge on IT-CSP-2 to 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -602,7 +603,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -791,7 +792,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Working independently and in a team are both structurally present - labs are team-based, and the robot rather than the teacher tells a student whether their fix worked, which forces independent troubleshooting. Discovery Systems 3 makes the cost of uncoordinated work explicit. The changing and diverse workplace framing is absent.</t>
+          <t>Working independently and in a team are both structurally present - labs are team-based, and the robot rather than the teacher tells a student whether their fix worked, which forces independent troubleshooting. Introductory Systems 3 makes the cost of uncoordinated work explicit. The changing and diverse workplace framing is absent.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1026,7 @@
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>Every lab is a program written to solve a stated physical problem, which is the first of Georgia's three routes. Nineteen reflection prompts address responsibility for automated-system errors (navigation misroute, spam misflag, freight misclassification). connects that work to systems that help or harm people, and Discovery Systems 12 asks whose responsibility it is to anticipate harm from a useful invention.</t>
+          <t>Every lab is a program written to solve a stated physical problem, which is the first of Georgia's three routes. Nineteen reflection prompts address responsibility for automated-system errors (navigation misroute, spam misflag, freight misclassification). connects that work to systems that help or harm people, and Introductory Systems 12 asks whose responsibility it is to anticipate harm from a useful invention.</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1650,7 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Discovery through computation is real - Unit 3.4's eight-turn test multiplies a small error until an invisible drift becomes visible, and Unit 5.4 sorts and searches recorded times to find best and worst runs. The tools are student-written rather than analytical software, and the connections found are within the student's own system.</t>
+          <t>Introductory through computation is real - Unit 3.4's eight-turn test multiplies a small error until an invisible drift becomes visible, and Unit 5.4 sorts and searches recorded times to find best and worst runs. The tools are student-written rather than analytical software, and the connections found are within the student's own system.</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1814,7 @@
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>Unit 1.1 defines algorithm as a stated objective and requires a precise step-by-step program that moves a robot to a target. Unit 3.5 plans a full multi-step mission before any code is written, and Discovery Systems 4 draws the plan and argues for doing so.</t>
+          <t>Unit 1.1 defines algorithm as a stated objective and requires a precise step-by-step program that moves a robot to a target. Unit 3.5 plans a full multi-step mission before any code is written, and Introductory Systems 4 draws the plan and argues for doing so.</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1943,7 @@
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Discovery Systems 4 compares a plan written as a list against the same plan drawn, and asks which is easier to check for a missing step - the natural-language-against-diagram comparison, in core but at the Discovery tier. Ext 1.1E (Blocks vs. Text) covers visual against textual, optionally. Pseudocode as a named format does not appear.</t>
+          <t>Introductory Systems 4 compares a plan written as a list against the same plan drawn, and asks which is easier to check for a missing step - the natural-language-against-diagram comparison, in core but at the Introductory tier. Ext 1.1E (Blocks vs. Text) covers visual against textual, optionally. Pseudocode as a named format does not appear.</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2322,7 @@
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Ext 5.3F (Talking to a Server) traces a file from the student's own machine across the internet to a remote server and asks what has to go right for that to work - address routing, server uptime, the local connection. Discovery Systems 9 covers senders, receivers, and protocols. Extension-weighted, and the layered abstraction view is not developed.</t>
+          <t>Ext 5.3F (Talking to a Server) traces a file from the student's own machine across the internet to a remote server and asks what has to go right for that to work - address routing, server uptime, the local connection. Introductory Systems 9 covers senders, receivers, and protocols. Extension-weighted, and the layered abstraction view is not developed.</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2486,7 @@
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Communication is covered through Discovery Systems 9 and Ext 5.3F (Talking to a Server); interaction through Ext 5.3H (Find the Community). COGNITION - how computing changes how people think - is not addressed, and it is the element Georgia distinguishes this from the other impacts standards by.</t>
+          <t>Communication is covered through Introductory Systems 9 and Ext 5.3F (Talking to a Server); interaction through Ext 5.3H (Find the Community). COGNITION - how computing changes how people think - is not addressed, and it is the element Georgia distinguishes this from the other impacts standards by.</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2572,7 @@
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>Nineteen reflection prompts address responsibility for automated-system errors (navigation misroute, spam misflag, freight misclassification). Discovery Systems 12 asks whose job it is to anticipate harm when something genuinely useful also causes harm. Ext 5.2D (Should It Exist?) requires a credible-source judgment on whether a real deployed system should exist, and Ext 2.6E (Automatic Data Collection) raises continuous collection nobody individually approves.</t>
+          <t>Nineteen reflection prompts address responsibility for automated-system errors (navigation misroute, spam misflag, freight misclassification). Introductory Systems 12 asks whose job it is to anticipate harm when something genuinely useful also causes harm. Ext 5.2D (Should It Exist?) requires a credible-source judgment on whether a real deployed system should exist, and Ext 2.6E (Automatic Data Collection) raises continuous collection nobody individually approves.</t>
         </is>
       </c>
     </row>
@@ -2930,6 +2931,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -2974,7 +2976,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2988,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -3122,6 +3124,8 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
@@ -3150,7 +3154,7 @@
 FBLA is the named career and technical student organization for this course. Worth knowing in a Georgia conversation: Botball Explorer is itself a competition programme, which is the natural bridge to IT-CSP-10 even though the curriculum does not supply that standard.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met.
 RESULT ON THE COMPUTER SCIENCE STANDARDS (IT-CSP-2 to 8, 44 elements): 16 Full, 27 Partial, 1 blank.
   IT-CSP-6 Create programs                4 Full, 2 Partial of 6   - strongest
